--- a/output/yearly_total_coral_cover_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_75_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.276602310021378</v>
+        <v>1.258557787217322</v>
       </c>
       <c r="C3" t="n">
-        <v>4.589922717573992</v>
+        <v>4.58418931098119</v>
       </c>
       <c r="D3" t="n">
-        <v>6.028456233031827</v>
+        <v>6.039589251997986</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8949812606272</v>
+        <v>11.8823363501965</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.44375427154337</v>
+        <v>1.388061903550102</v>
       </c>
       <c r="C4" t="n">
-        <v>5.00936224608088</v>
+        <v>4.992791936468517</v>
       </c>
       <c r="D4" t="n">
-        <v>6.199115482173629</v>
+        <v>6.346260084470689</v>
       </c>
       <c r="E4" t="n">
-        <v>12.65223199979788</v>
+        <v>12.72711392448931</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.669755397957256</v>
+        <v>1.561770929665384</v>
       </c>
       <c r="C5" t="n">
-        <v>5.514982791208165</v>
+        <v>5.505688220022267</v>
       </c>
       <c r="D5" t="n">
-        <v>6.429911404216823</v>
+        <v>6.684230651048526</v>
       </c>
       <c r="E5" t="n">
-        <v>13.61464959338224</v>
+        <v>13.75168980073618</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.938358107886053</v>
+        <v>1.765815117554819</v>
       </c>
       <c r="C6" t="n">
-        <v>6.142139254730592</v>
+        <v>6.150642009345467</v>
       </c>
       <c r="D6" t="n">
-        <v>6.761579778168359</v>
+        <v>7.15360905853983</v>
       </c>
       <c r="E6" t="n">
-        <v>14.842077140785</v>
+        <v>15.07006618544012</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.236203492403096</v>
+        <v>1.998520949855612</v>
       </c>
       <c r="C7" t="n">
-        <v>6.853736855809763</v>
+        <v>6.932525445886126</v>
       </c>
       <c r="D7" t="n">
-        <v>7.073477033441224</v>
+        <v>7.536268151504693</v>
       </c>
       <c r="E7" t="n">
-        <v>16.16341738165409</v>
+        <v>16.46731454724643</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.431630361164544</v>
+        <v>1.227938133514698</v>
       </c>
       <c r="C8" t="n">
-        <v>4.496113651051779</v>
+        <v>4.606029306301783</v>
       </c>
       <c r="D8" t="n">
-        <v>5.218455411185549</v>
+        <v>5.793136745602445</v>
       </c>
       <c r="E8" t="n">
-        <v>11.14619942340187</v>
+        <v>11.62710418541893</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.838131344637469</v>
+        <v>1.548499415520217</v>
       </c>
       <c r="C9" t="n">
-        <v>5.446588156194064</v>
+        <v>5.603756797626136</v>
       </c>
       <c r="D9" t="n">
-        <v>5.598471076266424</v>
+        <v>6.384484473560333</v>
       </c>
       <c r="E9" t="n">
-        <v>12.88319057709796</v>
+        <v>13.53674068670669</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.283185514038341</v>
+        <v>1.887346381151949</v>
       </c>
       <c r="C10" t="n">
-        <v>6.583164586958832</v>
+        <v>6.739639313812504</v>
       </c>
       <c r="D10" t="n">
-        <v>5.996734562645283</v>
+        <v>7.041354931337982</v>
       </c>
       <c r="E10" t="n">
-        <v>14.86308466364246</v>
+        <v>15.66834062630243</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.749551308436085</v>
+        <v>2.23864856524376</v>
       </c>
       <c r="C11" t="n">
-        <v>7.871858829458439</v>
+        <v>7.988492322569121</v>
       </c>
       <c r="D11" t="n">
-        <v>6.50795885971722</v>
+        <v>7.752145967623218</v>
       </c>
       <c r="E11" t="n">
-        <v>17.12936899761175</v>
+        <v>17.9792868554361</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.218935307969017</v>
+        <v>2.583356658575186</v>
       </c>
       <c r="C12" t="n">
-        <v>9.314730442880752</v>
+        <v>9.333696486407652</v>
       </c>
       <c r="D12" t="n">
-        <v>6.959720634820691</v>
+        <v>8.343244787472909</v>
       </c>
       <c r="E12" t="n">
-        <v>19.49338638567046</v>
+        <v>20.26029793245575</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.681573103709685</v>
+        <v>2.938940027945286</v>
       </c>
       <c r="C13" t="n">
-        <v>10.84108050567361</v>
+        <v>10.74798363055594</v>
       </c>
       <c r="D13" t="n">
-        <v>7.399687120827648</v>
+        <v>9.006324818684917</v>
       </c>
       <c r="E13" t="n">
-        <v>21.92234073021094</v>
+        <v>22.69324847718615</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.128723547118359</v>
+        <v>1.702595956090031</v>
       </c>
       <c r="C14" t="n">
-        <v>7.690422466446964</v>
+        <v>7.590706352126616</v>
       </c>
       <c r="D14" t="n">
-        <v>5.679518461315266</v>
+        <v>6.873304034725302</v>
       </c>
       <c r="E14" t="n">
-        <v>15.49866447488059</v>
+        <v>16.16660634294195</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.215186067431376</v>
+        <v>1.757730907160532</v>
       </c>
       <c r="C15" t="n">
-        <v>8.42684123687954</v>
+        <v>8.179195378483282</v>
       </c>
       <c r="D15" t="n">
-        <v>5.67957736617752</v>
+        <v>6.996650816286871</v>
       </c>
       <c r="E15" t="n">
-        <v>16.32160467048843</v>
+        <v>16.93357710193068</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.611655060314408</v>
+        <v>2.053178061276567</v>
       </c>
       <c r="C16" t="n">
-        <v>10.10488368288636</v>
+        <v>9.677872518924207</v>
       </c>
       <c r="D16" t="n">
-        <v>6.15606861443371</v>
+        <v>7.662933530728055</v>
       </c>
       <c r="E16" t="n">
-        <v>18.87260735763448</v>
+        <v>19.39398411092883</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.11448820540678</v>
+        <v>1.653577293216987</v>
       </c>
       <c r="C17" t="n">
-        <v>9.502286942019666</v>
+        <v>8.981371610146308</v>
       </c>
       <c r="D17" t="n">
-        <v>5.7157744040331</v>
+        <v>7.225574745963143</v>
       </c>
       <c r="E17" t="n">
-        <v>17.33254955145955</v>
+        <v>17.86052364932644</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.457942822260485</v>
+        <v>1.895695912038336</v>
       </c>
       <c r="C18" t="n">
-        <v>11.24940515649729</v>
+        <v>10.48409355112873</v>
       </c>
       <c r="D18" t="n">
-        <v>6.107599730275044</v>
+        <v>7.836143278188318</v>
       </c>
       <c r="E18" t="n">
-        <v>19.81494770903282</v>
+        <v>20.21593274135538</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.498302470382071</v>
+        <v>1.910127603290764</v>
       </c>
       <c r="C19" t="n">
-        <v>12.17859008865872</v>
+        <v>11.22489091632225</v>
       </c>
       <c r="D19" t="n">
-        <v>6.197174390810524</v>
+        <v>8.0543661578883</v>
       </c>
       <c r="E19" t="n">
-        <v>20.87406694985132</v>
+        <v>21.18938467750131</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.816751973208609</v>
+        <v>2.141829878970054</v>
       </c>
       <c r="C20" t="n">
-        <v>14.09742579408616</v>
+        <v>12.9233537145774</v>
       </c>
       <c r="D20" t="n">
-        <v>6.60515928426437</v>
+        <v>8.703105040854593</v>
       </c>
       <c r="E20" t="n">
-        <v>23.51933705155914</v>
+        <v>23.76828863440204</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.699346371188974</v>
+        <v>1.281553818169701</v>
       </c>
       <c r="C21" t="n">
-        <v>10.41084535491488</v>
+        <v>9.536677564099433</v>
       </c>
       <c r="D21" t="n">
-        <v>5.501792674415467</v>
+        <v>7.353103772744802</v>
       </c>
       <c r="E21" t="n">
-        <v>17.61198440051932</v>
+        <v>18.17133515501394</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_75_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.258557787217322</v>
+        <v>1.279095949190165</v>
       </c>
       <c r="C3" t="n">
-        <v>4.58418931098119</v>
+        <v>4.579152945258405</v>
       </c>
       <c r="D3" t="n">
-        <v>6.039589251997986</v>
+        <v>6.148681056893893</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8823363501965</v>
+        <v>12.00692995134246</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.388061903550102</v>
+        <v>1.448624133173749</v>
       </c>
       <c r="C4" t="n">
-        <v>4.992791936468517</v>
+        <v>5.020954124040075</v>
       </c>
       <c r="D4" t="n">
-        <v>6.346260084470689</v>
+        <v>6.480118863802927</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72711392448931</v>
+        <v>12.94969712101675</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.561770929665384</v>
+        <v>1.679533331320904</v>
       </c>
       <c r="C5" t="n">
-        <v>5.505688220022267</v>
+        <v>5.563365407686627</v>
       </c>
       <c r="D5" t="n">
-        <v>6.684230651048526</v>
+        <v>6.893338633149468</v>
       </c>
       <c r="E5" t="n">
-        <v>13.75168980073618</v>
+        <v>14.136237372157</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.765815117554819</v>
+        <v>1.934616025728662</v>
       </c>
       <c r="C6" t="n">
-        <v>6.150642009345467</v>
+        <v>6.24801182361563</v>
       </c>
       <c r="D6" t="n">
-        <v>7.15360905853983</v>
+        <v>7.307747937482095</v>
       </c>
       <c r="E6" t="n">
-        <v>15.07006618544012</v>
+        <v>15.49037578682639</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.998520949855612</v>
+        <v>2.229959591497716</v>
       </c>
       <c r="C7" t="n">
-        <v>6.932525445886126</v>
+        <v>7.05978802852639</v>
       </c>
       <c r="D7" t="n">
-        <v>7.536268151504693</v>
+        <v>7.691462526052608</v>
       </c>
       <c r="E7" t="n">
-        <v>16.46731454724643</v>
+        <v>16.98121014607672</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.227938133514698</v>
+        <v>1.437191755059738</v>
       </c>
       <c r="C8" t="n">
-        <v>4.606029306301783</v>
+        <v>4.726209847183317</v>
       </c>
       <c r="D8" t="n">
-        <v>5.793136745602445</v>
+        <v>6.009314206883873</v>
       </c>
       <c r="E8" t="n">
-        <v>11.62710418541893</v>
+        <v>12.17271580912693</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.548499415520217</v>
+        <v>1.832234102593189</v>
       </c>
       <c r="C9" t="n">
-        <v>5.603756797626136</v>
+        <v>5.724649591247002</v>
       </c>
       <c r="D9" t="n">
-        <v>6.384484473560333</v>
+        <v>6.588433983740551</v>
       </c>
       <c r="E9" t="n">
-        <v>13.53674068670669</v>
+        <v>14.14531767758074</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.887346381151949</v>
+        <v>2.247060522969767</v>
       </c>
       <c r="C10" t="n">
-        <v>6.739639313812504</v>
+        <v>6.836087800718802</v>
       </c>
       <c r="D10" t="n">
-        <v>7.041354931337982</v>
+        <v>7.173178794490562</v>
       </c>
       <c r="E10" t="n">
-        <v>15.66834062630243</v>
+        <v>16.25632711817913</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.23864856524376</v>
+        <v>2.675072397576547</v>
       </c>
       <c r="C11" t="n">
-        <v>7.988492322569121</v>
+        <v>8.088041064050179</v>
       </c>
       <c r="D11" t="n">
-        <v>7.752145967623218</v>
+        <v>7.747213006705437</v>
       </c>
       <c r="E11" t="n">
-        <v>17.9792868554361</v>
+        <v>18.51032646833216</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.583356658575186</v>
+        <v>3.110300071644096</v>
       </c>
       <c r="C12" t="n">
-        <v>9.333696486407652</v>
+        <v>9.420487807989041</v>
       </c>
       <c r="D12" t="n">
-        <v>8.343244787472909</v>
+        <v>8.349066047365229</v>
       </c>
       <c r="E12" t="n">
-        <v>20.26029793245575</v>
+        <v>20.87985392699836</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.938940027945286</v>
+        <v>3.525757772408602</v>
       </c>
       <c r="C13" t="n">
-        <v>10.74798363055594</v>
+        <v>10.84877037127724</v>
       </c>
       <c r="D13" t="n">
-        <v>9.006324818684917</v>
+        <v>8.959480325917612</v>
       </c>
       <c r="E13" t="n">
-        <v>22.69324847718615</v>
+        <v>23.33400846960346</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.702595956090031</v>
+        <v>2.027976597708551</v>
       </c>
       <c r="C14" t="n">
-        <v>7.590706352126616</v>
+        <v>7.701712565045803</v>
       </c>
       <c r="D14" t="n">
-        <v>6.873304034725302</v>
+        <v>6.764379126939118</v>
       </c>
       <c r="E14" t="n">
-        <v>16.16660634294195</v>
+        <v>16.49406828969347</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.757730907160532</v>
+        <v>2.092978113206733</v>
       </c>
       <c r="C15" t="n">
-        <v>8.179195378483282</v>
+        <v>8.337806537581397</v>
       </c>
       <c r="D15" t="n">
-        <v>6.996650816286871</v>
+        <v>6.860060258195012</v>
       </c>
       <c r="E15" t="n">
-        <v>16.93357710193068</v>
+        <v>17.29084490898314</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.053178061276567</v>
+        <v>2.438916551752181</v>
       </c>
       <c r="C16" t="n">
-        <v>9.677872518924207</v>
+        <v>9.915681265323913</v>
       </c>
       <c r="D16" t="n">
-        <v>7.662933530728055</v>
+        <v>7.456786147790309</v>
       </c>
       <c r="E16" t="n">
-        <v>19.39398411092883</v>
+        <v>19.8113839648664</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.653577293216987</v>
+        <v>1.959588052630719</v>
       </c>
       <c r="C17" t="n">
-        <v>8.981371610146308</v>
+        <v>9.24088679828691</v>
       </c>
       <c r="D17" t="n">
-        <v>7.225574745963143</v>
+        <v>6.98649954502496</v>
       </c>
       <c r="E17" t="n">
-        <v>17.86052364932644</v>
+        <v>18.18697439594259</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.895695912038336</v>
+        <v>2.243676385808618</v>
       </c>
       <c r="C18" t="n">
-        <v>10.48409355112873</v>
+        <v>10.85404553852006</v>
       </c>
       <c r="D18" t="n">
-        <v>7.836143278188318</v>
+        <v>7.485099751580786</v>
       </c>
       <c r="E18" t="n">
-        <v>20.21593274135538</v>
+        <v>20.58282167590946</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.910127603290764</v>
+        <v>2.257646655640051</v>
       </c>
       <c r="C19" t="n">
-        <v>11.22489091632225</v>
+        <v>11.68497716044047</v>
       </c>
       <c r="D19" t="n">
-        <v>8.0543661578883</v>
+        <v>7.634875181340681</v>
       </c>
       <c r="E19" t="n">
-        <v>21.18938467750131</v>
+        <v>21.5774989974212</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.141829878970054</v>
+        <v>2.51026997489684</v>
       </c>
       <c r="C20" t="n">
-        <v>12.9233537145774</v>
+        <v>13.53533596349669</v>
       </c>
       <c r="D20" t="n">
-        <v>8.703105040854593</v>
+        <v>8.119033879167038</v>
       </c>
       <c r="E20" t="n">
-        <v>23.76828863440204</v>
+        <v>24.16463981756057</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.281553818169701</v>
+        <v>1.492521582335299</v>
       </c>
       <c r="C21" t="n">
-        <v>9.536677564099433</v>
+        <v>10.06186349848626</v>
       </c>
       <c r="D21" t="n">
-        <v>7.353103772744802</v>
+        <v>6.801440102774435</v>
       </c>
       <c r="E21" t="n">
-        <v>18.17133515501394</v>
+        <v>18.355825183596</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_75_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.279095949190165</v>
+        <v>2.589251099587025</v>
       </c>
       <c r="C3" t="n">
-        <v>4.579152945258405</v>
+        <v>7.777638101848757</v>
       </c>
       <c r="D3" t="n">
-        <v>6.148681056893893</v>
+        <v>8.197708945242798</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00692995134246</v>
+        <v>18.56459814667858</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.448624133173749</v>
+        <v>1.060496367873403</v>
       </c>
       <c r="C4" t="n">
-        <v>5.020954124040075</v>
+        <v>4.676008042705297</v>
       </c>
       <c r="D4" t="n">
-        <v>6.480118863802927</v>
+        <v>5.816599417445375</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94969712101675</v>
+        <v>11.55310382802407</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.679533331320904</v>
+        <v>1.139604899791486</v>
       </c>
       <c r="C5" t="n">
-        <v>5.563365407686627</v>
+        <v>5.505106693776367</v>
       </c>
       <c r="D5" t="n">
-        <v>6.893338633149468</v>
+        <v>6.152826192713957</v>
       </c>
       <c r="E5" t="n">
-        <v>14.136237372157</v>
+        <v>12.79753778628181</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.934616025728662</v>
+        <v>1.221475657879345</v>
       </c>
       <c r="C6" t="n">
-        <v>6.24801182361563</v>
+        <v>6.560182049851917</v>
       </c>
       <c r="D6" t="n">
-        <v>7.307747937482095</v>
+        <v>6.566511949508778</v>
       </c>
       <c r="E6" t="n">
-        <v>15.49037578682639</v>
+        <v>14.34816965724004</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.229959591497716</v>
+        <v>1.302360094775191</v>
       </c>
       <c r="C7" t="n">
-        <v>7.05978802852639</v>
+        <v>7.79015505446006</v>
       </c>
       <c r="D7" t="n">
-        <v>7.691462526052608</v>
+        <v>6.977416952502877</v>
       </c>
       <c r="E7" t="n">
-        <v>16.98121014607672</v>
+        <v>16.06993210173813</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.437191755059738</v>
+        <v>1.383660154901935</v>
       </c>
       <c r="C8" t="n">
-        <v>4.726209847183317</v>
+        <v>9.224267799307645</v>
       </c>
       <c r="D8" t="n">
-        <v>6.009314206883873</v>
+        <v>7.366792933983906</v>
       </c>
       <c r="E8" t="n">
-        <v>12.17271580912693</v>
+        <v>17.97472088819348</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.832234102593189</v>
+        <v>1.455431690575568</v>
       </c>
       <c r="C9" t="n">
-        <v>5.724649591247002</v>
+        <v>10.85296257983446</v>
       </c>
       <c r="D9" t="n">
-        <v>6.588433983740551</v>
+        <v>7.78018971048449</v>
       </c>
       <c r="E9" t="n">
-        <v>14.14531767758074</v>
+        <v>20.08858398089452</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.247060522969767</v>
+        <v>0.9321203577971341</v>
       </c>
       <c r="C10" t="n">
-        <v>6.836087800718802</v>
+        <v>7.897306160162894</v>
       </c>
       <c r="D10" t="n">
-        <v>7.173178794490562</v>
+        <v>6.117417207317513</v>
       </c>
       <c r="E10" t="n">
-        <v>16.25632711817913</v>
+        <v>14.94684372527754</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.675072397576547</v>
+        <v>0.8421726331340412</v>
       </c>
       <c r="C11" t="n">
-        <v>8.088041064050179</v>
+        <v>8.705284520758019</v>
       </c>
       <c r="D11" t="n">
-        <v>7.747213006705437</v>
+        <v>5.975397584421168</v>
       </c>
       <c r="E11" t="n">
-        <v>18.51032646833216</v>
+        <v>15.52285473831323</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.110300071644096</v>
+        <v>0.8759251192060467</v>
       </c>
       <c r="C12" t="n">
-        <v>9.420487807989041</v>
+        <v>10.48421136085324</v>
       </c>
       <c r="D12" t="n">
-        <v>8.349066047365229</v>
+        <v>6.370011074143174</v>
       </c>
       <c r="E12" t="n">
-        <v>20.87985392699836</v>
+        <v>17.73014755420246</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.525757772408602</v>
+        <v>0.6769248595552183</v>
       </c>
       <c r="C13" t="n">
-        <v>10.84877037127724</v>
+        <v>10.07650135675658</v>
       </c>
       <c r="D13" t="n">
-        <v>8.959480325917612</v>
+        <v>5.809344777724864</v>
       </c>
       <c r="E13" t="n">
-        <v>23.33400846960346</v>
+        <v>16.56277099403666</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.027976597708551</v>
+        <v>0.7098330426015714</v>
       </c>
       <c r="C14" t="n">
-        <v>7.701712565045803</v>
+        <v>11.88335891903763</v>
       </c>
       <c r="D14" t="n">
-        <v>6.764379126939118</v>
+        <v>6.138897847086433</v>
       </c>
       <c r="E14" t="n">
-        <v>16.49406828969347</v>
+        <v>18.73208980872563</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.092978113206733</v>
+        <v>0.6686389089313752</v>
       </c>
       <c r="C15" t="n">
-        <v>8.337806537581397</v>
+        <v>12.86108145769702</v>
       </c>
       <c r="D15" t="n">
-        <v>6.860060258195012</v>
+        <v>6.157796490393185</v>
       </c>
       <c r="E15" t="n">
-        <v>17.29084490898314</v>
+        <v>19.68751685702158</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.438916551752181</v>
+        <v>0.717353230016102</v>
       </c>
       <c r="C16" t="n">
-        <v>9.915681265323913</v>
+        <v>14.92121029271966</v>
       </c>
       <c r="D16" t="n">
-        <v>7.456786147790309</v>
+        <v>6.533069550341527</v>
       </c>
       <c r="E16" t="n">
-        <v>19.8113839648664</v>
+        <v>22.17163307307728</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.959588052630719</v>
+        <v>0.4292397312507905</v>
       </c>
       <c r="C17" t="n">
-        <v>9.24088679828691</v>
+        <v>11.02124699003033</v>
       </c>
       <c r="D17" t="n">
-        <v>6.98649954502496</v>
+        <v>5.414289501535946</v>
       </c>
       <c r="E17" t="n">
-        <v>18.18697439594259</v>
+        <v>16.86477622281707</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.243676385808618</v>
+        <v>0.3287185838129595</v>
       </c>
       <c r="C18" t="n">
-        <v>10.85404553852006</v>
+        <v>9.865621949884368</v>
       </c>
       <c r="D18" t="n">
-        <v>7.485099751580786</v>
+        <v>4.910436944762399</v>
       </c>
       <c r="E18" t="n">
-        <v>20.58282167590946</v>
+        <v>15.10477747845973</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.257646655640051</v>
+        <v>0.3784244700789756</v>
       </c>
       <c r="C19" t="n">
-        <v>11.68497716044047</v>
+        <v>12.15790466453024</v>
       </c>
       <c r="D19" t="n">
-        <v>7.634875181340681</v>
+        <v>5.373085550388708</v>
       </c>
       <c r="E19" t="n">
-        <v>21.5774989974212</v>
+        <v>17.90941468499793</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.51026997489684</v>
+        <v>0.424007015987155</v>
       </c>
       <c r="C20" t="n">
-        <v>13.53533596349669</v>
+        <v>14.54227531383447</v>
       </c>
       <c r="D20" t="n">
-        <v>8.119033879167038</v>
+        <v>5.781423873016085</v>
       </c>
       <c r="E20" t="n">
-        <v>24.16463981756057</v>
+        <v>20.74770620283771</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.492521582335299</v>
+        <v>0.4673413596526092</v>
       </c>
       <c r="C21" t="n">
-        <v>10.06186349848626</v>
+        <v>17.09409285157504</v>
       </c>
       <c r="D21" t="n">
-        <v>6.801440102774435</v>
+        <v>6.171000997015304</v>
       </c>
       <c r="E21" t="n">
-        <v>18.355825183596</v>
+        <v>23.73243520824295</v>
       </c>
     </row>
   </sheetData>
